--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2560,6 +2560,117 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121576037</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99602</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>718</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Glesgröe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Glyceria lithuanica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Gorski) Gorski</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Torsboda NB, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628720</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6935474</v>
+      </c>
+      <c r="S19" t="n">
+        <v>125</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Y-Tim-0161</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2009-11-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2009-11-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -2565,7 +2565,7 @@
         <v>121576037</v>
       </c>
       <c r="B19" t="n">
-        <v>99602</v>
+        <v>99603</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -2565,7 +2565,7 @@
         <v>121576037</v>
       </c>
       <c r="B19" t="n">
-        <v>99603</v>
+        <v>99611</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -2565,7 +2565,7 @@
         <v>121576037</v>
       </c>
       <c r="B19" t="n">
-        <v>99611</v>
+        <v>99629</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2560,117 +2560,6 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>121576037</v>
-      </c>
-      <c r="B19" t="n">
-        <v>99629</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>718</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Glesgröe</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Glyceria lithuanica</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Gorski) Gorski</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Torsboda NB, Mpd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>628720</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6935474</v>
-      </c>
-      <c r="S19" t="n">
-        <v>125</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Hässjö</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Y-Tim-0161</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Via Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98151350</v>
+        <v>107523760</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>718</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Glesgröe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Glyceria lithuanica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Gorski) Gorski</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gryttjom, Mpd</t>
+          <t>Torsboda NB, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629345.5487011154</v>
+        <v>628720</v>
       </c>
       <c r="R2" t="n">
-        <v>6935978.001884451</v>
+        <v>6935475</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-11-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-11-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +760,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98151195</v>
+        <v>121576037</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>718</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Glesgröe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Glyceria lithuanica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gorski) Gorski</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gryttjom, Mpd</t>
+          <t>Torsboda NB, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628997.1030825613</v>
+        <v>628720</v>
       </c>
       <c r="R3" t="n">
-        <v>6935918.70159923</v>
+        <v>6935474</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,24 +839,19 @@
           <t>Hässjö</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Y-Tim-0161</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-11-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-11-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +866,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98150994</v>
+        <v>98151196</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629085.5820213337</v>
+        <v>629153</v>
       </c>
       <c r="R4" t="n">
-        <v>6935975.740276041</v>
+        <v>6935839</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +950,9 @@
           <t>2021-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98151352</v>
+        <v>98150994</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628750.0699612694</v>
+        <v>629085</v>
       </c>
       <c r="R5" t="n">
-        <v>6935916.96902841</v>
+        <v>6935976</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,22 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1076,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98151354</v>
+        <v>114565671</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gryttjom, Mpd</t>
+          <t>Torsboda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629282.0631122262</v>
+        <v>629391</v>
       </c>
       <c r="R6" t="n">
-        <v>6935742.638417224</v>
+        <v>6935982</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1141,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,65 +1161,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98151196</v>
+        <v>114565672</v>
       </c>
       <c r="B7" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gryttjom, Mpd</t>
+          <t>Torsboda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629152.9136437996</v>
+        <v>629394</v>
       </c>
       <c r="R7" t="n">
-        <v>6935838.811350852</v>
+        <v>6935984</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1238,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,65 +1258,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107523764</v>
+        <v>114565674</v>
       </c>
       <c r="B8" t="n">
-        <v>96943</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222302</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Torsboda NB, Mpd</t>
+          <t>Torsboda, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628719.5591434144</v>
+        <v>629376</v>
       </c>
       <c r="R8" t="n">
-        <v>6935474.479561071</v>
+        <v>6936006</v>
       </c>
       <c r="S8" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1335,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,69 +1355,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107523761</v>
+        <v>114565675</v>
       </c>
       <c r="B9" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torsboda NB, Mpd</t>
+          <t>Torsboda, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628719.5591434144</v>
+        <v>629369</v>
       </c>
       <c r="R9" t="n">
-        <v>6935474.479561071</v>
+        <v>6936010</v>
       </c>
       <c r="S9" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,22 +1432,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,69 +1452,72 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107523760</v>
+        <v>116713245</v>
       </c>
       <c r="B10" t="n">
-        <v>97792</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>718</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Glesgröe</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glyceria lithuanica</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gorski) Gorski</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Torsboda NB, Mpd</t>
+          <t>Gryttjom, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628719.5591434144</v>
+        <v>628702</v>
       </c>
       <c r="R10" t="n">
-        <v>6935474.479561071</v>
+        <v>6935047</v>
       </c>
       <c r="S10" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,22 +1541,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2009-11-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Trummande och ropande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,31 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110180386</v>
+        <v>114565673</v>
       </c>
       <c r="B11" t="n">
-        <v>5219</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,46 +1589,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102147</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rumpgärdan, Mpd</t>
+          <t>Torsboda, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628707.583461264</v>
+        <v>629396</v>
       </c>
       <c r="R11" t="n">
-        <v>6935234.160547456</v>
+        <v>6935992</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,22 +1643,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,49 +1663,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Heimdahl</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Heimdahl, Mattias Edman</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114565672</v>
+        <v>114565676</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629394</v>
+        <v>629372</v>
       </c>
       <c r="R12" t="n">
-        <v>6935984</v>
+        <v>6936000</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1918,53 +1772,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114565676</v>
+        <v>118019319</v>
       </c>
       <c r="B13" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>101256</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre purpurmätare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lythria cruentaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Torsboda, Mpd</t>
+          <t>Rumpgärdan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629372</v>
+        <v>628386</v>
       </c>
       <c r="R13" t="n">
-        <v>6936000</v>
+        <v>6935346</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,12 +1850,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,33 +1864,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114565671</v>
+        <v>117814366</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,37 +1894,54 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>101298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotnätfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Melitaea diamina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Lang, 1789)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Torsboda, Mpd</t>
+          <t>Rumpgärdan, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629391</v>
+        <v>628381</v>
       </c>
       <c r="R14" t="n">
-        <v>6935982</v>
+        <v>6935434</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,71 +1979,76 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114565674</v>
+        <v>110180386</v>
       </c>
       <c r="B15" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102147</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schrank, 1781)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Torsboda, Mpd</t>
+          <t>Rumpgärdan, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>629376</v>
+        <v>628708</v>
       </c>
       <c r="R15" t="n">
-        <v>6936006</v>
+        <v>6935234</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,12 +2072,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-06-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-06-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,65 +2102,77 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Stefan Heimdahl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Stefan Heimdahl, Mattias Edman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114565673</v>
+        <v>110406795</v>
       </c>
       <c r="B16" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>201129</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torsboda, Mpd</t>
+          <t>Gryttjom, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629396</v>
+        <v>628546</v>
       </c>
       <c r="R16" t="n">
-        <v>6935992</v>
+        <v>6935137</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,12 +2196,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,85 +2210,64 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Joel Hallqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Joel Hallqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117814366</v>
+        <v>98151195</v>
       </c>
       <c r="B17" t="n">
-        <v>42926</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101298</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotnätfjäril</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Melitaea diamina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lang, 1789)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rumpgärdan, Mpd</t>
+          <t>Gryttjom, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628381</v>
+        <v>628997</v>
       </c>
       <c r="R17" t="n">
-        <v>6935434</v>
+        <v>6935919</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2413,12 +2294,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,85 +2308,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118019319</v>
+        <v>107523764</v>
       </c>
       <c r="B18" t="n">
-        <v>41229</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99771</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101256</v>
+        <v>222302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre purpurmätare</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lythria cruentaria</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rumpgärdan, Mpd</t>
+          <t>Torsboda NB, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628386</v>
+        <v>628720</v>
       </c>
       <c r="R18" t="n">
-        <v>6935346</v>
+        <v>6935475</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,12 +2391,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2009-11-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2009-11-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,22 +2405,616 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>107523761</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Torsboda NB, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628720</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6935475</v>
+      </c>
+      <c r="S19" t="n">
+        <v>125</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2009-11-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2009-11-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Engström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>98151349</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gryttjom, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>629098</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6935947</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>98151350</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gryttjom, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>629345</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6935978</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>98151352</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gryttjom, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>628750</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6935917</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>98151353</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gryttjom, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>629095</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6935876</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>98151354</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gryttjom, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>629282</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6935742</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37600-2022 artfynd.xlsx
+++ b/artfynd/A 37600-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107523760</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121576037</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98151196</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98150994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565671</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565672</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565674</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565675</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116713245</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565673</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565676</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118019319</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117814366</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110180386</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2226,6 +2301,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110406795</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2323,6 +2403,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98151195</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2424,6 +2509,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107523764</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2525,6 +2615,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107523761</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2627,6 +2722,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98151349</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2724,6 +2824,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98151350</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2821,6 +2926,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98151352</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2918,6 +3028,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98151353</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3015,8 +3130,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98151354</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>